--- a/artfynd/A 24431-2025 artfynd.xlsx
+++ b/artfynd/A 24431-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125561570</v>
+        <v>125565330</v>
       </c>
       <c r="B2" t="n">
         <v>57635</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604050</v>
+        <v>604005</v>
       </c>
       <c r="R2" t="n">
-        <v>6937055</v>
+        <v>6936979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125565330</v>
+        <v>125565043</v>
       </c>
       <c r="B4" t="n">
         <v>57635</v>
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,7 +947,7 @@
         <v>604005</v>
       </c>
       <c r="R4" t="n">
-        <v>6936979</v>
+        <v>6937107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125565043</v>
+        <v>125561570</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604005</v>
+        <v>604050</v>
       </c>
       <c r="R5" t="n">
-        <v>6937107</v>
+        <v>6937055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24431-2025 artfynd.xlsx
+++ b/artfynd/A 24431-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125565330</v>
+        <v>125561570</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604005</v>
+        <v>604050</v>
       </c>
       <c r="R2" t="n">
-        <v>6936979</v>
+        <v>6937055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,12 +785,7 @@
         <v>125561669</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,12 +892,7 @@
         <v>125565043</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125561570</v>
+        <v>125565330</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1027,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604050</v>
+        <v>604005</v>
       </c>
       <c r="R5" t="n">
-        <v>6937055</v>
+        <v>6936979</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24431-2025 artfynd.xlsx
+++ b/artfynd/A 24431-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125561570</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125561669</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>125565043</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125565330</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24431-2025 artfynd.xlsx
+++ b/artfynd/A 24431-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125561570</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125561669</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>125565043</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125565330</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24431-2025 artfynd.xlsx
+++ b/artfynd/A 24431-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125561570</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125561669</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>125565043</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>125565330</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24431-2025 artfynd.xlsx
+++ b/artfynd/A 24431-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125561570</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125561669</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125565043</v>
+        <v>125561890</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604005</v>
+        <v>604114</v>
       </c>
       <c r="R4" t="n">
-        <v>6937107</v>
+        <v>6937157</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125565330</v>
+        <v>125562495</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604005</v>
+        <v>604063</v>
       </c>
       <c r="R5" t="n">
-        <v>6936979</v>
+        <v>6937173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,6 +1100,434 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125564928</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>604027</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6937156</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125565043</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>604005</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6937107</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125565330</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>604005</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6936979</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125565383</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>604000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6936964</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24431-2025 artfynd.xlsx
+++ b/artfynd/A 24431-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561570</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561669</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561890</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564928</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565043</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565330</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,8 +1568,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565383</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>